--- a/docs/StructureDefinition-autonomous-medical-encounter.xlsx
+++ b/docs/StructureDefinition-autonomous-medical-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-autonomous-medical-encounter.xlsx
+++ b/docs/StructureDefinition-autonomous-medical-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-autonomous-medical-encounter.xlsx
+++ b/docs/StructureDefinition-autonomous-medical-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -483,7 +483,7 @@
     <t>Links to specific Mars mission</t>
   </si>
   <si>
-    <t>Links radiation exposure to specific space missions</t>
+    <t>Links clinical observations and events to specific space missions</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>

--- a/docs/StructureDefinition-autonomous-medical-encounter.xlsx
+++ b/docs/StructureDefinition-autonomous-medical-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-autonomous-medical-encounter.xlsx
+++ b/docs/StructureDefinition-autonomous-medical-encounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2746" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/autonomous-medical-encounter</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/autonomous-medical-encounter</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -456,7 +459,7 @@
     <t>communicationDelay</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/communication-delay}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/communication-delay}
 </t>
   </si>
   <si>
@@ -476,7 +479,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -1754,54 +1757,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1824,7 +1829,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.01171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1857,143 +1862,143 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2005,13 +2010,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -2062,25 +2067,25 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>20</v>
@@ -2091,10 +2096,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2102,10 +2107,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2114,19 +2119,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2176,13 +2181,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2216,10 +2221,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2228,16 +2233,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2288,19 +2293,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2317,10 +2322,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2328,31 +2333,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2402,19 +2407,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2431,10 +2436,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2442,10 +2447,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2457,16 +2462,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2492,13 +2497,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2516,19 +2521,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2545,21 +2550,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2571,16 +2576,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2630,25 +2635,25 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>20</v>
@@ -2659,21 +2664,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2685,16 +2690,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2744,13 +2749,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2762,7 +2767,7 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>20</v>
@@ -2773,10 +2778,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2784,10 +2789,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2799,13 +2804,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2844,29 +2849,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2883,26 +2888,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2911,13 +2916,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2968,19 +2973,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2997,26 +3002,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -3025,13 +3030,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3082,19 +3087,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3111,45 +3116,45 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3198,25 +3203,25 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>20</v>
@@ -3227,10 +3232,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3238,10 +3243,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3250,16 +3255,16 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3310,39 +3315,39 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3350,31 +3355,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3400,13 +3405,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3424,39 +3429,39 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3464,10 +3469,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3479,16 +3484,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3538,25 +3543,25 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
@@ -3567,10 +3572,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3578,10 +3583,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3593,13 +3598,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3650,13 +3655,13 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
@@ -3668,7 +3673,7 @@
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -3679,21 +3684,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3705,16 +3710,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3764,25 +3769,25 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
@@ -3793,45 +3798,45 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3880,25 +3885,25 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>20</v>
@@ -3909,10 +3914,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3920,10 +3925,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3935,13 +3940,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3968,13 +3973,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3992,25 +3997,25 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -4021,10 +4026,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4032,10 +4037,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4047,13 +4052,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4104,25 +4109,25 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
@@ -4133,10 +4138,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4144,28 +4149,28 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4192,13 +4197,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4216,39 +4221,39 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4256,10 +4261,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4271,13 +4276,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4328,25 +4333,25 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
@@ -4357,10 +4362,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4368,10 +4373,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4383,13 +4388,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4440,13 +4445,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4458,7 +4463,7 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4469,21 +4474,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4495,16 +4500,16 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4554,25 +4559,25 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -4583,45 +4588,45 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4670,25 +4675,25 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
@@ -4699,10 +4704,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4710,10 +4715,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4725,13 +4730,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4758,13 +4763,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4782,25 +4787,25 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4811,10 +4816,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4822,10 +4827,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4837,13 +4842,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4894,25 +4899,25 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4923,10 +4928,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4934,10 +4939,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4946,19 +4951,19 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4984,13 +4989,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5008,39 +5013,39 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5048,10 +5053,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5060,16 +5065,16 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5096,13 +5101,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5120,39 +5125,39 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5160,10 +5165,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5175,13 +5180,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5208,13 +5213,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5232,71 +5237,71 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5346,39 +5351,39 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5386,10 +5391,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5398,16 +5403,16 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5458,50 +5463,50 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5513,13 +5518,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5570,25 +5575,25 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5599,10 +5604,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5610,10 +5615,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5622,16 +5627,16 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5682,39 +5687,39 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5722,10 +5727,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5737,13 +5742,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5794,13 +5799,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5812,7 +5817,7 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -5823,21 +5828,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5849,16 +5854,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5908,25 +5913,25 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
@@ -5937,45 +5942,45 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6024,25 +6029,25 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
@@ -6053,10 +6058,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6064,10 +6069,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6076,19 +6081,19 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6114,13 +6119,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6138,39 +6143,39 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6178,10 +6183,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6193,13 +6198,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6250,39 +6255,39 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6290,10 +6295,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6302,16 +6307,16 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6362,39 +6367,39 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6402,10 +6407,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6414,16 +6419,16 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6474,39 +6479,39 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6514,13 +6519,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
@@ -6529,16 +6534,16 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6588,39 +6593,39 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6628,10 +6633,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6643,16 +6648,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6702,71 +6707,71 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6792,13 +6797,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6816,50 +6821,50 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6868,19 +6873,19 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6930,39 +6935,39 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6970,28 +6975,28 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7042,25 +7047,25 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
@@ -7071,10 +7076,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7082,10 +7087,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7097,13 +7102,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7154,13 +7159,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -7172,7 +7177,7 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7183,21 +7188,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7209,16 +7214,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7268,25 +7273,25 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7297,45 +7302,45 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7384,25 +7389,25 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7413,21 +7418,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7436,19 +7441,19 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7498,39 +7503,39 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7538,10 +7543,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7553,13 +7558,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7586,13 +7591,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7610,25 +7615,25 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
@@ -7639,10 +7644,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7650,10 +7655,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7665,13 +7670,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7722,25 +7727,25 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -7751,10 +7756,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7762,10 +7767,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7777,16 +7782,16 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7836,25 +7841,25 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
@@ -7865,10 +7870,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7876,10 +7881,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7891,16 +7896,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7950,25 +7955,25 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
@@ -7979,10 +7984,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7990,10 +7995,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8005,13 +8010,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8062,13 +8067,13 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
@@ -8080,7 +8085,7 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -8091,21 +8096,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8117,16 +8122,16 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8176,25 +8181,25 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8205,45 +8210,45 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8292,25 +8297,25 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8321,10 +8326,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8332,10 +8337,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8347,13 +8352,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8404,39 +8409,39 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8444,10 +8449,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8459,13 +8464,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8516,25 +8521,25 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
@@ -8545,10 +8550,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8556,10 +8561,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -8571,13 +8576,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8604,13 +8609,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8628,39 +8633,39 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8668,10 +8673,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8683,13 +8688,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8716,13 +8721,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8740,39 +8745,39 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8780,10 +8785,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -8795,19 +8800,19 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8832,13 +8837,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -8856,39 +8861,39 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8896,10 +8901,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -8911,13 +8916,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8944,13 +8949,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -8968,39 +8973,39 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9008,10 +9013,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9023,13 +9028,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9056,13 +9061,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9080,39 +9085,39 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9120,10 +9125,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9135,13 +9140,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9192,39 +9197,39 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9232,10 +9237,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9247,13 +9252,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9280,13 +9285,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9304,39 +9309,39 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9344,10 +9349,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9359,16 +9364,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9418,25 +9423,25 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9447,10 +9452,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9458,10 +9463,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -9473,13 +9478,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9530,13 +9535,13 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
@@ -9548,7 +9553,7 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
@@ -9559,21 +9564,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -9585,16 +9590,16 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9644,25 +9649,25 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
@@ -9673,45 +9678,45 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9760,25 +9765,25 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
@@ -9789,10 +9794,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9800,10 +9805,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -9815,13 +9820,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9872,39 +9877,39 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9912,10 +9917,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -9927,16 +9932,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9962,13 +9967,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -9986,25 +9991,25 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>20</v>
@@ -10015,10 +10020,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10026,10 +10031,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10041,16 +10046,16 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10076,13 +10081,13 @@
         <v>20</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -10100,19 +10105,19 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -10129,10 +10134,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10140,10 +10145,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -10155,13 +10160,13 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10212,25 +10217,25 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
@@ -10241,10 +10246,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10252,10 +10257,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -10267,13 +10272,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10324,39 +10329,39 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10364,10 +10369,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -10379,16 +10384,16 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10438,25 +10443,25 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>20</v>
